--- a/application/tests/Fixtures/Ndi/tires_valid.xlsx
+++ b/application/tests/Fixtures/Ndi/tires_valid.xlsx
@@ -581,7 +581,7 @@
       </x:c>
       <x:c r="AF2" s="21"/>
       <x:c r="AG2" s="21" t="str">
-        <x:v>https://example.invalid/TEST-TIRE-001.png</x:v>
+        <x:v>https://example.invalid/Imagev2.aspx?id=11111111-1111-4111-8111-111111111111</x:v>
       </x:c>
       <x:c r="AH2" s="21" t="str">
         <x:v>TEST-DOT25</x:v>
@@ -679,7 +679,7 @@
       </x:c>
       <x:c r="AF3" s="23"/>
       <x:c r="AG3" s="23" t="str">
-        <x:v>https://example.invalid/TEST-TIRE-002.png</x:v>
+        <x:v>https://example.invalid/Imagev2.aspx?id=22222222-2222-4222-8222-222222222222</x:v>
       </x:c>
       <x:c r="AH3" s="23"/>
     </x:row>
@@ -757,7 +757,7 @@
       </x:c>
       <x:c r="AF4" s="25"/>
       <x:c r="AG4" s="25" t="str">
-        <x:v>https://example.invalid/TEST-TIRE-003.png</x:v>
+        <x:v>https://example.invalid/Imagev2.aspx?id=33333333-3333-4333-8333-333333333333</x:v>
       </x:c>
       <x:c r="AH4" s="25"/>
     </x:row>
